--- a/importacaoV5.xlsx
+++ b/importacaoV5.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
   <si>
     <t>CAMPO</t>
   </si>
@@ -265,17 +265,29 @@
     <t>i</t>
   </si>
   <si>
-    <t>07A</t>
-  </si>
-  <si>
-    <t>07X</t>
+    <t>06X</t>
+  </si>
+  <si>
+    <t>LINHA_CIRCULAR</t>
+  </si>
+  <si>
+    <t>texto</t>
+  </si>
+  <si>
+    <t>true | false</t>
+  </si>
+  <si>
+    <t>hora | inteiro</t>
+  </si>
+  <si>
+    <t>true</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -321,6 +333,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="11">
@@ -450,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -555,6 +574,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1354,7 +1376,9 @@
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
+      <c r="E2" s="46" t="s">
+        <v>81</v>
+      </c>
       <c r="F2" s="43" t="s">
         <v>67</v>
       </c>
@@ -1528,7 +1552,9 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
+      <c r="E3" s="46" t="s">
+        <v>81</v>
+      </c>
       <c r="F3" s="43">
         <v>410</v>
       </c>
@@ -1584,7 +1610,9 @@
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
+      <c r="E4" s="46" t="s">
+        <v>81</v>
+      </c>
       <c r="F4" s="43">
         <v>20</v>
       </c>
@@ -1674,7 +1702,9 @@
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
+      <c r="E5" s="46" t="s">
+        <v>81</v>
+      </c>
       <c r="F5" s="43">
         <v>61</v>
       </c>
@@ -1768,7 +1798,9 @@
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
+      <c r="E6" s="46" t="s">
+        <v>83</v>
+      </c>
       <c r="F6" s="43">
         <v>5</v>
       </c>
@@ -1862,7 +1894,9 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
+      <c r="E7" s="46" t="s">
+        <v>83</v>
+      </c>
       <c r="F7" s="44">
         <v>1.5277777777777777E-2</v>
       </c>
@@ -1944,7 +1978,9 @@
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
+      <c r="E8" s="46" t="s">
+        <v>83</v>
+      </c>
       <c r="F8" s="44">
         <v>1.5277777777777777E-2</v>
       </c>
@@ -2034,7 +2070,9 @@
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
+      <c r="E9" s="46" t="s">
+        <v>81</v>
+      </c>
       <c r="F9" s="43">
         <v>51</v>
       </c>
@@ -2118,12 +2156,18 @@
       <c r="AV9" s="18"/>
     </row>
     <row r="10" spans="1:48" x14ac:dyDescent="0.3">
-      <c r="A10" s="13"/>
+      <c r="A10" s="13" t="s">
+        <v>80</v>
+      </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="43"/>
+      <c r="E10" s="46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" s="43" t="s">
+        <v>84</v>
+      </c>
       <c r="G10" s="40"/>
       <c r="H10" s="20"/>
       <c r="I10" s="19">
@@ -2204,7 +2248,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
+      <c r="E11" s="46"/>
       <c r="F11" s="43"/>
       <c r="G11" s="40"/>
       <c r="H11" s="20"/>
@@ -3506,7 +3550,9 @@
       <c r="L35" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="M35" s="37"/>
+      <c r="M35" s="37" t="s">
+        <v>79</v>
+      </c>
       <c r="N35" s="37"/>
       <c r="O35" s="37"/>
       <c r="P35" s="37">
@@ -3581,12 +3627,8 @@
       </c>
       <c r="J37" s="37"/>
       <c r="K37" s="45"/>
-      <c r="L37" s="36" t="s">
-        <v>79</v>
-      </c>
-      <c r="M37" s="37" t="s">
-        <v>80</v>
-      </c>
+      <c r="L37" s="36"/>
+      <c r="M37" s="37"/>
       <c r="N37" s="37"/>
       <c r="O37" s="37"/>
       <c r="P37" s="37"/>

--- a/importacaoV5.xlsx
+++ b/importacaoV5.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="86">
   <si>
     <t>CAMPO</t>
   </si>
@@ -280,7 +280,10 @@
     <t>hora | inteiro</t>
   </si>
   <si>
-    <t>true</t>
+    <t>false</t>
+  </si>
+  <si>
+    <t>02A</t>
   </si>
 </sst>
 </file>
@@ -342,7 +345,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,12 +398,6 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor rgb="FFD9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -469,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -541,9 +538,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1205,9 +1199,9 @@
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="38" t="s">
+      <c r="F1" s="41"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="37" t="s">
         <v>34</v>
       </c>
       <c r="I1" s="11">
@@ -1376,14 +1370,14 @@
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="40"/>
-      <c r="H2" s="38" t="s">
+      <c r="G2" s="39"/>
+      <c r="H2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="I2" s="11" t="s">
@@ -1552,14 +1546,14 @@
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
       <c r="D3" s="13"/>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F3" s="43">
+      <c r="F3" s="42">
         <v>410</v>
       </c>
-      <c r="G3" s="40"/>
-      <c r="H3" s="38" t="s">
+      <c r="G3" s="39"/>
+      <c r="H3" s="37" t="s">
         <v>40</v>
       </c>
       <c r="I3" s="14"/>
@@ -1610,13 +1604,13 @@
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
       <c r="D4" s="13"/>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="42">
         <v>20</v>
       </c>
-      <c r="G4" s="40"/>
+      <c r="G4" s="39"/>
       <c r="H4" s="20"/>
       <c r="I4" s="16">
         <v>0.20833333333333334</v>
@@ -1702,13 +1696,13 @@
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="42">
         <v>61</v>
       </c>
-      <c r="G5" s="40"/>
+      <c r="G5" s="39"/>
       <c r="H5" s="20"/>
       <c r="I5" s="19">
         <v>0.2638888888888889</v>
@@ -1798,13 +1792,13 @@
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="42">
         <v>5</v>
       </c>
-      <c r="G6" s="40"/>
+      <c r="G6" s="39"/>
       <c r="H6" s="20"/>
       <c r="I6" s="19">
         <v>0.3263888888888889</v>
@@ -1894,13 +1888,13 @@
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
       <c r="D7" s="13"/>
-      <c r="E7" s="46" t="s">
+      <c r="E7" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="44">
+      <c r="F7" s="43">
         <v>1.5277777777777777E-2</v>
       </c>
-      <c r="G7" s="41"/>
+      <c r="G7" s="40"/>
       <c r="H7" s="20"/>
       <c r="I7" s="19">
         <v>0.38958333333333334</v>
@@ -1978,13 +1972,13 @@
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
       <c r="D8" s="13"/>
-      <c r="E8" s="46" t="s">
+      <c r="E8" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="44">
+      <c r="F8" s="43">
         <v>1.5277777777777777E-2</v>
       </c>
-      <c r="G8" s="41"/>
+      <c r="G8" s="40"/>
       <c r="H8" s="20"/>
       <c r="I8" s="19">
         <v>0.45277777777777778</v>
@@ -2070,13 +2064,13 @@
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
-      <c r="E9" s="46" t="s">
+      <c r="E9" s="45" t="s">
         <v>81</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="42">
         <v>51</v>
       </c>
-      <c r="G9" s="40"/>
+      <c r="G9" s="39"/>
       <c r="H9" s="20"/>
       <c r="I9" s="19">
         <v>0.51597222222222228</v>
@@ -2162,13 +2156,13 @@
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
-      <c r="E10" s="46" t="s">
+      <c r="E10" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="F10" s="43" t="s">
+      <c r="F10" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="40"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="20"/>
       <c r="I10" s="19">
         <v>0.57569444444444462</v>
@@ -2248,9 +2242,9 @@
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="40"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="20"/>
       <c r="I11" s="19"/>
       <c r="J11" s="17"/>
@@ -2331,8 +2325,8 @@
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="43"/>
-      <c r="G12" s="40"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="39"/>
       <c r="H12" s="20"/>
       <c r="I12" s="19">
         <v>0.64930555555555558</v>
@@ -2413,8 +2407,8 @@
       <c r="C13" s="13"/>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
-      <c r="F13" s="43"/>
-      <c r="G13" s="40"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="39"/>
       <c r="H13" s="20"/>
       <c r="I13" s="19">
         <v>0.72430555555555554</v>
@@ -2483,8 +2477,8 @@
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
-      <c r="F14" s="43"/>
-      <c r="G14" s="40"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="39"/>
       <c r="H14" s="20"/>
       <c r="I14" s="19">
         <v>0.8041666666666667</v>
@@ -2549,8 +2543,8 @@
       <c r="C15" s="13"/>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="40"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="39"/>
       <c r="H15" s="20"/>
       <c r="I15" s="19">
         <v>0.86111111111111116</v>
@@ -2611,8 +2605,8 @@
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="40"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="39"/>
       <c r="H16" s="20"/>
       <c r="I16" s="19">
         <v>0.91666666666666674</v>
@@ -2673,8 +2667,8 @@
       <c r="C17" s="13"/>
       <c r="D17" s="13"/>
       <c r="E17" s="13"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="40"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="39"/>
       <c r="H17" s="20"/>
       <c r="I17" s="19">
         <v>0.96527777777777712</v>
@@ -2731,8 +2725,8 @@
       <c r="C18" s="13"/>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="40"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="39"/>
       <c r="H18" s="20"/>
       <c r="I18" s="19"/>
       <c r="J18" s="17"/>
@@ -2781,8 +2775,8 @@
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="40"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="39"/>
       <c r="H19" s="20"/>
       <c r="I19" s="19"/>
       <c r="J19" s="17"/>
@@ -2831,8 +2825,8 @@
       <c r="C20" s="13"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="40"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="39"/>
       <c r="H20" s="20"/>
       <c r="I20" s="19"/>
       <c r="J20" s="17"/>
@@ -2881,8 +2875,8 @@
       <c r="C21" s="13"/>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="40"/>
+      <c r="F21" s="42"/>
+      <c r="G21" s="39"/>
       <c r="H21" s="20"/>
       <c r="I21" s="19"/>
       <c r="J21" s="17"/>
@@ -2931,8 +2925,8 @@
       <c r="C22" s="13"/>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="40"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="39"/>
       <c r="H22" s="20"/>
       <c r="I22" s="19"/>
       <c r="J22" s="17"/>
@@ -2981,8 +2975,8 @@
       <c r="C23" s="13"/>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="40"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="39"/>
       <c r="H23" s="20"/>
       <c r="I23" s="19"/>
       <c r="J23" s="17"/>
@@ -3031,8 +3025,8 @@
       <c r="C24" s="13"/>
       <c r="D24" s="13"/>
       <c r="E24" s="13"/>
-      <c r="F24" s="43"/>
-      <c r="G24" s="40"/>
+      <c r="F24" s="42"/>
+      <c r="G24" s="39"/>
       <c r="H24" s="20"/>
       <c r="I24" s="19"/>
       <c r="J24" s="17"/>
@@ -3081,8 +3075,8 @@
       <c r="C25" s="13"/>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
-      <c r="F25" s="43"/>
-      <c r="G25" s="40"/>
+      <c r="F25" s="42"/>
+      <c r="G25" s="39"/>
       <c r="H25" s="20"/>
       <c r="I25" s="19"/>
       <c r="J25" s="17"/>
@@ -3131,8 +3125,8 @@
       <c r="C26" s="13"/>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
-      <c r="F26" s="43"/>
-      <c r="G26" s="40"/>
+      <c r="F26" s="42"/>
+      <c r="G26" s="39"/>
       <c r="H26" s="20"/>
       <c r="I26" s="19"/>
       <c r="J26" s="17"/>
@@ -3181,8 +3175,8 @@
       <c r="C27" s="13"/>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
-      <c r="F27" s="43"/>
-      <c r="G27" s="40"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="39"/>
       <c r="H27" s="20"/>
       <c r="I27" s="19"/>
       <c r="J27" s="17"/>
@@ -3231,8 +3225,8 @@
       <c r="C28" s="13"/>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
-      <c r="F28" s="43"/>
-      <c r="G28" s="40"/>
+      <c r="F28" s="42"/>
+      <c r="G28" s="39"/>
       <c r="H28" s="20"/>
       <c r="I28" s="19"/>
       <c r="J28" s="17"/>
@@ -3447,9 +3441,6 @@
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
       <c r="G33" s="10"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
       <c r="L33" s="32" t="s">
         <v>73</v>
       </c>
@@ -3485,15 +3476,6 @@
       <c r="G34" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="H34" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="J34" s="33" t="s">
-        <v>65</v>
-      </c>
       <c r="L34" s="24" t="s">
         <v>68</v>
       </c>
@@ -3524,569 +3506,498 @@
       <c r="U34" s="25"/>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A35" s="34">
+      <c r="A35" s="33">
         <v>2</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="34">
         <v>0.22222222222222221</v>
       </c>
-      <c r="C35" s="36" t="s">
+      <c r="C35" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="36"/>
-      <c r="E35" s="37"/>
-      <c r="F35" s="37">
+      <c r="D35" s="35"/>
+      <c r="E35" s="36"/>
+      <c r="F35" s="36">
         <v>57</v>
       </c>
-      <c r="G35" s="37" t="s">
+      <c r="G35" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H35" s="37"/>
-      <c r="I35" s="37">
+      <c r="K35" s="44"/>
+      <c r="L35" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="M35" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" s="36"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="36">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="36"/>
+      <c r="R35" s="36"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="36"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="33">
+        <v>3</v>
+      </c>
+      <c r="B36" s="34">
+        <v>0.23611111111111113</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="35"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36">
+        <v>57</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="K36" s="44"/>
+      <c r="L36" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="36"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="33">
+        <v>5</v>
+      </c>
+      <c r="B37" s="34">
+        <v>0.25694444444444448</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="35"/>
+      <c r="E37" s="36"/>
+      <c r="F37" s="36">
+        <v>57</v>
+      </c>
+      <c r="G37" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="K37" s="44"/>
+      <c r="L37" s="35" t="s">
+        <v>85</v>
+      </c>
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
+      <c r="S37" s="36">
         <v>30</v>
       </c>
-      <c r="J35" s="37"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="M35" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="N35" s="37"/>
-      <c r="O35" s="37"/>
-      <c r="P35" s="37">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="37"/>
-      <c r="R35" s="37"/>
-      <c r="S35" s="37"/>
-      <c r="T35" s="37"/>
-      <c r="U35" s="37"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A36" s="34">
-        <v>3</v>
-      </c>
-      <c r="B36" s="35">
-        <v>0.23611111111111113</v>
-      </c>
-      <c r="C36" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="D36" s="36"/>
-      <c r="E36" s="37"/>
-      <c r="F36" s="37">
+      <c r="T37" s="36"/>
+      <c r="U37" s="36"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="33">
+        <v>6</v>
+      </c>
+      <c r="B38" s="34">
+        <v>0.25694444444444448</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="D38" s="35"/>
+      <c r="E38" s="36"/>
+      <c r="F38" s="36">
         <v>57</v>
       </c>
-      <c r="G36" s="37" t="s">
+      <c r="G38" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H36" s="37"/>
-      <c r="I36" s="37">
-        <v>30</v>
-      </c>
-      <c r="J36" s="37"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="M36" s="37"/>
-      <c r="N36" s="37"/>
-      <c r="O36" s="37"/>
-      <c r="P36" s="37">
-        <v>3</v>
-      </c>
-      <c r="Q36" s="37"/>
-      <c r="R36" s="37"/>
-      <c r="S36" s="37"/>
-      <c r="T36" s="37"/>
-      <c r="U36" s="37"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="34">
-        <v>5</v>
-      </c>
-      <c r="B37" s="35">
-        <v>0.25694444444444448</v>
-      </c>
-      <c r="C37" s="36" t="s">
+      <c r="K38" s="44"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36"/>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="36"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="33">
+        <v>8</v>
+      </c>
+      <c r="B39" s="34">
+        <v>0.27777777777777779</v>
+      </c>
+      <c r="C39" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D37" s="36"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37">
+      <c r="D39" s="35"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36">
         <v>57</v>
       </c>
-      <c r="G37" s="37" t="s">
+      <c r="G39" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H37" s="37"/>
-      <c r="I37" s="37">
-        <v>30</v>
-      </c>
-      <c r="J37" s="37"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="37"/>
-      <c r="N37" s="37"/>
-      <c r="O37" s="37"/>
-      <c r="P37" s="37"/>
-      <c r="Q37" s="37"/>
-      <c r="R37" s="37"/>
-      <c r="S37" s="37"/>
-      <c r="T37" s="37"/>
-      <c r="U37" s="37"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="34">
-        <v>6</v>
-      </c>
-      <c r="B38" s="35">
-        <v>0.25694444444444448</v>
-      </c>
-      <c r="C38" s="36" t="s">
+      <c r="K39" s="44"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36"/>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="36"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="33">
+        <v>10</v>
+      </c>
+      <c r="B40" s="34">
+        <v>0.22916666666666666</v>
+      </c>
+      <c r="C40" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D38" s="36"/>
-      <c r="E38" s="37"/>
-      <c r="F38" s="37">
+      <c r="D40" s="35"/>
+      <c r="E40" s="36"/>
+      <c r="F40" s="36">
         <v>57</v>
       </c>
-      <c r="G38" s="37" t="s">
+      <c r="G40" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37">
-        <v>30</v>
-      </c>
-      <c r="J38" s="37"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="37"/>
-      <c r="N38" s="37"/>
-      <c r="O38" s="37"/>
-      <c r="P38" s="37"/>
-      <c r="Q38" s="37"/>
-      <c r="R38" s="37"/>
-      <c r="S38" s="37"/>
-      <c r="T38" s="37"/>
-      <c r="U38" s="37"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A39" s="34">
-        <v>8</v>
-      </c>
-      <c r="B39" s="35">
-        <v>0.27777777777777779</v>
-      </c>
-      <c r="C39" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D39" s="36"/>
-      <c r="E39" s="37"/>
-      <c r="F39" s="37">
-        <v>57</v>
-      </c>
-      <c r="G39" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="H39" s="37"/>
-      <c r="I39" s="37">
-        <v>30</v>
-      </c>
-      <c r="J39" s="37"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
-      <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A40" s="34">
-        <v>10</v>
-      </c>
-      <c r="B40" s="35">
-        <v>0.22916666666666666</v>
-      </c>
-      <c r="C40" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="D40" s="36"/>
-      <c r="E40" s="37"/>
-      <c r="F40" s="37">
-        <v>57</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>77</v>
-      </c>
-      <c r="H40" s="37"/>
-      <c r="I40" s="37">
-        <v>30</v>
-      </c>
-      <c r="J40" s="37"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="37"/>
-      <c r="N40" s="37"/>
-      <c r="O40" s="37"/>
-      <c r="P40" s="37"/>
-      <c r="Q40" s="37"/>
-      <c r="R40" s="37"/>
-      <c r="S40" s="37"/>
-      <c r="T40" s="37"/>
-      <c r="U40" s="37"/>
+      <c r="K40" s="44"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="36"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A41" s="34"/>
-      <c r="B41" s="35"/>
-      <c r="C41" s="36"/>
-      <c r="D41" s="36"/>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="37"/>
+      <c r="A41" s="33"/>
+      <c r="B41" s="34"/>
+      <c r="C41" s="35"/>
+      <c r="D41" s="35"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="K41" s="44"/>
+      <c r="L41" s="35"/>
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="36"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A42" s="34"/>
-      <c r="B42" s="35"/>
-      <c r="C42" s="36"/>
-      <c r="D42" s="36"/>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="37"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="37"/>
-      <c r="N42" s="37"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="37"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-      <c r="U42" s="37"/>
+      <c r="A42" s="33"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="K42" s="44"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="36"/>
+      <c r="P42" s="36"/>
+      <c r="Q42" s="36"/>
+      <c r="R42" s="36"/>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="36"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A43" s="34"/>
-      <c r="B43" s="35"/>
-      <c r="C43" s="36"/>
-      <c r="D43" s="36"/>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="37"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="37"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-      <c r="U43" s="37"/>
+      <c r="A43" s="33"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="36"/>
+      <c r="F43" s="36"/>
+      <c r="G43" s="36"/>
+      <c r="K43" s="44"/>
+      <c r="L43" s="35"/>
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="36"/>
+      <c r="P43" s="36"/>
+      <c r="Q43" s="36"/>
+      <c r="R43" s="36"/>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+      <c r="U43" s="36"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A44" s="34"/>
-      <c r="B44" s="35"/>
-      <c r="C44" s="36"/>
-      <c r="D44" s="36"/>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="37"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
-      <c r="O44" s="37"/>
-      <c r="P44" s="37"/>
-      <c r="Q44" s="37"/>
-      <c r="R44" s="37"/>
-      <c r="S44" s="37"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="37"/>
+      <c r="A44" s="33"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="36"/>
+      <c r="F44" s="36"/>
+      <c r="G44" s="36"/>
+      <c r="K44" s="44"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36"/>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="36"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A45" s="34"/>
-      <c r="B45" s="35"/>
-      <c r="C45" s="36"/>
-      <c r="D45" s="36"/>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="37"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="36"/>
-      <c r="M45" s="37"/>
-      <c r="N45" s="37"/>
-      <c r="O45" s="37"/>
-      <c r="P45" s="37"/>
-      <c r="Q45" s="37"/>
-      <c r="R45" s="37"/>
-      <c r="S45" s="37"/>
-      <c r="T45" s="37"/>
-      <c r="U45" s="37"/>
+      <c r="A45" s="33"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="36"/>
+      <c r="F45" s="36"/>
+      <c r="G45" s="36"/>
+      <c r="K45" s="44"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="36"/>
+      <c r="P45" s="36"/>
+      <c r="Q45" s="36"/>
+      <c r="R45" s="36"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="36"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A46" s="34"/>
-      <c r="B46" s="35"/>
-      <c r="C46" s="36"/>
-      <c r="D46" s="36"/>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="37"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="37"/>
-      <c r="N46" s="37"/>
-      <c r="O46" s="37"/>
-      <c r="P46" s="37"/>
-      <c r="Q46" s="37"/>
-      <c r="R46" s="37"/>
-      <c r="S46" s="37"/>
-      <c r="T46" s="37"/>
-      <c r="U46" s="37"/>
+      <c r="A46" s="33"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="36"/>
+      <c r="F46" s="36"/>
+      <c r="G46" s="36"/>
+      <c r="K46" s="44"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="36"/>
+      <c r="P46" s="36"/>
+      <c r="Q46" s="36"/>
+      <c r="R46" s="36"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+      <c r="U46" s="36"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A47" s="34"/>
-      <c r="B47" s="35"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="37"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="36"/>
-      <c r="M47" s="37"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
+      <c r="A47" s="33"/>
+      <c r="B47" s="34"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="36"/>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="36"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A48" s="34"/>
-      <c r="B48" s="35"/>
-      <c r="C48" s="36"/>
-      <c r="D48" s="36"/>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="37"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="36"/>
-      <c r="M48" s="37"/>
-      <c r="N48" s="37"/>
-      <c r="O48" s="37"/>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="37"/>
-      <c r="S48" s="37"/>
-      <c r="T48" s="37"/>
-      <c r="U48" s="37"/>
+      <c r="A48" s="33"/>
+      <c r="B48" s="34"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36"/>
+      <c r="R48" s="36"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="36"/>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A49" s="34"/>
-      <c r="B49" s="35"/>
-      <c r="C49" s="36"/>
-      <c r="D49" s="36"/>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="37"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="37"/>
-      <c r="N49" s="37"/>
-      <c r="O49" s="37"/>
-      <c r="P49" s="37"/>
-      <c r="Q49" s="37"/>
-      <c r="R49" s="37"/>
-      <c r="S49" s="37"/>
-      <c r="T49" s="37"/>
-      <c r="U49" s="37"/>
+      <c r="A49" s="33"/>
+      <c r="B49" s="34"/>
+      <c r="C49" s="35"/>
+      <c r="D49" s="35"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
+      <c r="G49" s="36"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="36"/>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A50" s="34"/>
-      <c r="B50" s="35"/>
-      <c r="C50" s="36"/>
-      <c r="D50" s="36"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="36"/>
-      <c r="M50" s="37"/>
-      <c r="N50" s="37"/>
-      <c r="O50" s="37"/>
-      <c r="P50" s="37"/>
-      <c r="Q50" s="37"/>
-      <c r="R50" s="37"/>
-      <c r="S50" s="37"/>
-      <c r="T50" s="37"/>
-      <c r="U50" s="37"/>
+      <c r="A50" s="33"/>
+      <c r="B50" s="34"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
+      <c r="E50" s="36"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="K50" s="44"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="36"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36"/>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36"/>
+      <c r="U50" s="36"/>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A51" s="34"/>
-      <c r="B51" s="35"/>
-      <c r="C51" s="36"/>
-      <c r="D51" s="36"/>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37"/>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37"/>
-      <c r="I51" s="37"/>
-      <c r="J51" s="37"/>
-      <c r="K51" s="45"/>
-      <c r="L51" s="36"/>
-      <c r="M51" s="37"/>
-      <c r="N51" s="37"/>
-      <c r="O51" s="37"/>
-      <c r="P51" s="37"/>
-      <c r="Q51" s="37"/>
-      <c r="R51" s="37"/>
-      <c r="S51" s="37"/>
-      <c r="T51" s="37"/>
-      <c r="U51" s="37"/>
+      <c r="A51" s="33"/>
+      <c r="B51" s="34"/>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="K51" s="44"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="36"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36"/>
+      <c r="U51" s="36"/>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A52" s="34"/>
-      <c r="B52" s="35"/>
-      <c r="C52" s="36"/>
-      <c r="D52" s="36"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37"/>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="37"/>
-      <c r="K52" s="45"/>
-      <c r="L52" s="36"/>
-      <c r="M52" s="37"/>
-      <c r="N52" s="37"/>
-      <c r="O52" s="37"/>
-      <c r="P52" s="37"/>
-      <c r="Q52" s="37"/>
-      <c r="R52" s="37"/>
-      <c r="S52" s="37"/>
-      <c r="T52" s="37"/>
-      <c r="U52" s="37"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="35"/>
+      <c r="E52" s="36"/>
+      <c r="F52" s="36"/>
+      <c r="G52" s="36"/>
+      <c r="K52" s="44"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="36"/>
+      <c r="N52" s="36"/>
+      <c r="O52" s="36"/>
+      <c r="P52" s="36"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="36"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36"/>
+      <c r="U52" s="36"/>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A53" s="34"/>
-      <c r="B53" s="35"/>
-      <c r="C53" s="36"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37"/>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="37"/>
-      <c r="K53" s="45"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="37"/>
-      <c r="N53" s="37"/>
-      <c r="O53" s="37"/>
-      <c r="P53" s="37"/>
-      <c r="Q53" s="37"/>
-      <c r="R53" s="37"/>
-      <c r="S53" s="37"/>
-      <c r="T53" s="37"/>
-      <c r="U53" s="37"/>
+      <c r="A53" s="33"/>
+      <c r="B53" s="34"/>
+      <c r="C53" s="35"/>
+      <c r="D53" s="35"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="36"/>
+      <c r="U53" s="36"/>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A54" s="34"/>
-      <c r="B54" s="35"/>
-      <c r="C54" s="36"/>
-      <c r="D54" s="36"/>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37"/>
-      <c r="I54" s="37"/>
-      <c r="J54" s="37"/>
-      <c r="K54" s="45"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="37"/>
-      <c r="N54" s="37"/>
-      <c r="O54" s="37"/>
-      <c r="P54" s="37"/>
-      <c r="Q54" s="37"/>
-      <c r="R54" s="37"/>
-      <c r="S54" s="37"/>
-      <c r="T54" s="37"/>
-      <c r="U54" s="37"/>
+      <c r="A54" s="33"/>
+      <c r="B54" s="34"/>
+      <c r="C54" s="35"/>
+      <c r="D54" s="35"/>
+      <c r="E54" s="36"/>
+      <c r="F54" s="36"/>
+      <c r="G54" s="36"/>
+      <c r="K54" s="44"/>
+      <c r="L54" s="35"/>
+      <c r="M54" s="36"/>
+      <c r="N54" s="36"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36"/>
+      <c r="R54" s="36"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36"/>
+      <c r="U54" s="36"/>
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A55" s="34"/>
-      <c r="B55" s="35"/>
-      <c r="C55" s="36"/>
-      <c r="D55" s="36"/>
-      <c r="E55" s="37"/>
-      <c r="F55" s="37"/>
-      <c r="G55" s="37"/>
-      <c r="H55" s="37"/>
-      <c r="I55" s="37"/>
-      <c r="J55" s="37"/>
-      <c r="K55" s="45"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="37"/>
-      <c r="N55" s="37"/>
-      <c r="O55" s="37"/>
-      <c r="P55" s="37"/>
-      <c r="Q55" s="37"/>
-      <c r="R55" s="37"/>
-      <c r="S55" s="37"/>
-      <c r="T55" s="37"/>
-      <c r="U55" s="37"/>
+      <c r="A55" s="33"/>
+      <c r="B55" s="34"/>
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="36"/>
+      <c r="F55" s="36"/>
+      <c r="G55" s="36"/>
+      <c r="K55" s="44"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="36"/>
+      <c r="N55" s="36"/>
+      <c r="O55" s="36"/>
+      <c r="P55" s="36"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36"/>
+      <c r="T55" s="36"/>
+      <c r="U55" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.51180555555555596" right="0.51180555555555596" top="0.78749999999999998" bottom="0.78749999999999998" header="0.511811023622047" footer="0.511811023622047"/>
